--- a/연구코드/aec/results/강남/logistic_results.xlsx
+++ b/연구코드/aec/results/강남/logistic_results.xlsx
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>217473871818.365</v>
+        <v>217473878827.7454</v>
       </c>
       <c r="F10" t="n">
         <v>15.7361</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.699137147922753e+31</v>
+        <v>1.699137376042557e+31</v>
       </c>
       <c r="F12" t="n">
         <v>40.6982</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>115308986.9962</v>
+        <v>115308987.6496</v>
       </c>
       <c r="F13" t="n">
         <v>9.762</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>5.482749553451126e+17</v>
+        <v>5.482749880061208e+17</v>
       </c>
       <c r="F16" t="n">
         <v>23.89</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.304604097987171e+49</v>
+        <v>1.30460441715463e+49</v>
       </c>
       <c r="F17" t="n">
         <v>62.3713</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.95718576571727e+163</v>
+        <v>1.95718771375254e+163</v>
       </c>
       <c r="F18" t="n">
         <v>197.9569</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>9.083629393035032e+51</v>
+        <v>9.083631727057405e+51</v>
       </c>
       <c r="F23" t="n">
         <v>65.79649999999999</v>
@@ -1328,7 +1328,7 @@
         <v>15.0399</v>
       </c>
       <c r="C24" t="n">
-        <v>3402110.5322</v>
+        <v>3402110.5545</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>11.6828</v>
       </c>
       <c r="C26" t="n">
-        <v>118513.8274</v>
+        <v>118513.828</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>8.090970313194803e+45</v>
+        <v>8.090972069683324e+45</v>
       </c>
       <c r="F33" t="n">
         <v>58.4414</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>4.168247429080646e+40</v>
+        <v>4.168248213930226e+40</v>
       </c>
       <c r="F34" t="n">
         <v>52.1026</v>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.968356071724979e+19</v>
+        <v>1.968356210021403e+19</v>
       </c>
       <c r="F35" t="n">
         <v>25.9442</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>9.852496779102026e+50</v>
+        <v>9.852499195344899e+50</v>
       </c>
       <c r="F36" t="n">
         <v>64.55549999999999</v>
@@ -1726,7 +1726,7 @@
         <v>23.8806</v>
       </c>
       <c r="C38" t="n">
-        <v>23506857561.9763</v>
+        <v>23506857810.2528</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>33203.1824</v>
+        <v>33203.1864</v>
       </c>
       <c r="G38" t="n">
         <v>0.0007</v>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7522</v>
+        <v>0.7518</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7262</v>
+        <v>0.7268</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.777</v>
+        <v>0.7778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/연구코드/aec/results/강남/logistic_results.xlsx
+++ b/연구코드/aec/results/강남/logistic_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,23 +509,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AEC: p25 (표준화)</t>
+          <t>AEC: mean (표준화)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5879</v>
+        <v>0.5863</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5191</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6659</v>
+        <v>0.6615</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6454</v>
+        <v>0.6526999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -597,50 +597,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AEC: mean (표준화)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.5863</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.5197000000000001</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.6615</v>
+          <t>ManufacturerModelName (LR χ²-test)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LR_χ²=50.59</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.01076</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6526999999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ManufacturerModelName (LR χ²-test)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LR_χ²=50.59</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01076</v>
-      </c>
-      <c r="F9" t="n">
         <v>0.5809</v>
       </c>
     </row>
@@ -655,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,25 +685,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.4103</v>
+        <v>-1.3968</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2441</v>
+        <v>0.2474</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0409</v>
+        <v>0.0411</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4553</v>
+        <v>1.4905</v>
       </c>
       <c r="F2" t="n">
-        <v>0.911</v>
+        <v>0.9163</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.5481</v>
+        <v>-1.5244</v>
       </c>
       <c r="H2" t="n">
-        <v>0.121597</v>
+        <v>0.127408</v>
       </c>
     </row>
     <row r="3">
@@ -735,25 +713,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.141</v>
+        <v>0.1205</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1514</v>
+        <v>1.1281</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8612</v>
+        <v>0.846</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5394</v>
+        <v>1.5042</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1482</v>
+        <v>0.1468</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9516</v>
+        <v>0.8209</v>
       </c>
       <c r="H3" t="n">
-        <v>0.341292</v>
+        <v>0.411709</v>
       </c>
     </row>
     <row r="4">
@@ -763,22 +741,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6054</v>
+        <v>0.6039</v>
       </c>
       <c r="C4" t="n">
-        <v>1.832</v>
+        <v>1.8293</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5849</v>
+        <v>1.5822</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1176</v>
+        <v>2.1149</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="G4" t="n">
-        <v>8.1892</v>
+        <v>8.158300000000001</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -787,29 +765,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6352</v>
+        <v>-0.9557</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5298</v>
+        <v>0.3846</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1757</v>
+        <v>0.3154</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5979</v>
+        <v>0.4688</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5632</v>
+        <v>0.1011</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1278</v>
+        <v>-9.4513</v>
       </c>
       <c r="H5" t="n">
-        <v>0.259399</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -819,25 +797,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0047</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9954</v>
+        <v>1.1004</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7832</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.265</v>
+        <v>1.2965</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1223</v>
+        <v>0.0837</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0381</v>
+        <v>1.1436</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9696399999999999</v>
+        <v>0.252804</v>
       </c>
     </row>
     <row r="7">
@@ -847,25 +825,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0604</v>
+        <v>0.1228</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0623</v>
+        <v>1.1306</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8761</v>
+        <v>0.9644</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2881</v>
+        <v>1.3255</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0983</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6143999999999999</v>
+        <v>1.5135</v>
       </c>
       <c r="H7" t="n">
-        <v>0.538936</v>
+        <v>0.130156</v>
       </c>
     </row>
     <row r="8">
@@ -875,858 +853,860 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2572</v>
+        <v>0.2727</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2932</v>
+        <v>1.3135</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0539</v>
+        <v>1.0742</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5869</v>
+        <v>1.6062</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1044</v>
+        <v>0.1026</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4629</v>
+        <v>2.6578</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01378</v>
+        <v>0.007865</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean_z</t>
+          <t>Model_Aquilion ONE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3981</v>
+        <v>-4.3405</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6716</v>
+        <v>0.013</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2505</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8008</v>
+        <v>4907710998.3521</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5032</v>
+        <v>13.5995</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7911</v>
+        <v>-0.3192</v>
       </c>
       <c r="H9" t="n">
-        <v>0.428908</v>
+        <v>0.749599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Model_Aquilion ONE</t>
+          <t>Model_Aquilion PRIME</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-4.7368</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.4698</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.0269</v>
       </c>
       <c r="E10" t="n">
-        <v>217473878827.7454</v>
+        <v>8.197800000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>15.7361</v>
+        <v>1.4589</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.301</v>
+        <v>-0.5179</v>
       </c>
       <c r="H10" t="n">
-        <v>0.763402</v>
+        <v>0.604542</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Model_Aquilion PRIME</t>
+          <t>Model_BrightSpeed</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-7.931</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4717</v>
+        <v>0.0004</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0273</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8.162699999999999</v>
+        <v>1.352319893368584e+31</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4546</v>
+        <v>40.6196</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.1953</v>
       </c>
       <c r="H11" t="n">
-        <v>0.605434</v>
+        <v>0.845197</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Model_BrightSpeed</t>
+          <t>Model_BrightSpeed S</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-7.8568</v>
+        <v>-0.4449</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0004</v>
+        <v>0.6409</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.699137376042557e+31</v>
+        <v>126016823.9013</v>
       </c>
       <c r="F12" t="n">
-        <v>40.6982</v>
+        <v>9.743399999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1931</v>
+        <v>-0.0457</v>
       </c>
       <c r="H12" t="n">
-        <v>0.84692</v>
+        <v>0.963583</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Model_BrightSpeed S</t>
+          <t>Model_Brilliance 64</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5701000000000001</v>
+        <v>0.204</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5655</v>
+        <v>1.2263</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>115308987.6496</v>
+        <v>16.5665</v>
       </c>
       <c r="F13" t="n">
-        <v>9.762</v>
+        <v>1.3283</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0584</v>
+        <v>0.1536</v>
       </c>
       <c r="H13" t="n">
-        <v>0.953433</v>
+        <v>0.8779130000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Model_Brilliance 64</t>
+          <t>Model_Brivo CT385 Series</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1835</v>
+        <v>-0.092</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2015</v>
+        <v>0.9121</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0295</v>
       </c>
       <c r="E14" t="n">
-        <v>16.1555</v>
+        <v>28.2168</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3259</v>
+        <v>1.751</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1384</v>
+        <v>-0.0525</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8899010000000001</v>
+        <v>0.958098</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Model_Brivo CT385 Series</t>
+          <t>Model_Discovery CT750 HD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1139</v>
+        <v>-5.8296</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8923</v>
+        <v>0.0029</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0287</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>27.6975</v>
+        <v>2.333850588485075e+16</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7527</v>
+        <v>22.2037</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.065</v>
+        <v>-0.2626</v>
       </c>
       <c r="H15" t="n">
-        <v>0.94818</v>
+        <v>0.792896</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model_Discovery CT750 HD</t>
+          <t>Model_Emotion 16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-5.9779</v>
+        <v>-8.7902</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0025</v>
+        <v>0.0002</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>5.482749880061208e+17</v>
+        <v>7.902220908476959e+41</v>
       </c>
       <c r="F16" t="n">
-        <v>23.89</v>
+        <v>53.7068</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2502</v>
+        <v>-0.1637</v>
       </c>
       <c r="H16" t="n">
-        <v>0.802412</v>
+        <v>0.86999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Model_Emotion 16</t>
+          <t>Model_Emotion 6</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-9.153</v>
+        <v>-11.7783</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.30460441715463e+49</v>
+        <v>1.992487879582542e+147</v>
       </c>
       <c r="F17" t="n">
-        <v>62.3713</v>
+        <v>179.0582</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1467</v>
+        <v>-0.0658</v>
       </c>
       <c r="H17" t="n">
-        <v>0.883329</v>
+        <v>0.947554</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model_Emotion 6</t>
+          <t>Model_IQon - Spectral CT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-11.9955</v>
+        <v>-0.5198</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5946</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.0245</v>
       </c>
       <c r="E18" t="n">
-        <v>1.95718771375254e+163</v>
+        <v>14.4276</v>
       </c>
       <c r="F18" t="n">
-        <v>197.9569</v>
+        <v>1.627</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0606</v>
+        <v>-0.3195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.951681</v>
+        <v>0.74937</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Model_IQon - Spectral CT</t>
+          <t>Model_Ingenuity CT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.5284</v>
+        <v>-13.8837</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5895</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0241</v>
-      </c>
-      <c r="E19" t="n">
-        <v>14.3973</v>
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>1.6304</v>
+        <v>422.8457</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3241</v>
+        <v>-0.0328</v>
       </c>
       <c r="H19" t="n">
-        <v>0.745842</v>
+        <v>0.973807</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT</t>
+          <t>Model_Ingenuity Core 128</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-13.8853</v>
+        <v>-0.2787</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.7568</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.1241</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4.613</v>
       </c>
       <c r="F20" t="n">
-        <v>427.4985</v>
+        <v>0.9223</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0325</v>
+        <v>-0.3022</v>
       </c>
       <c r="H20" t="n">
-        <v>0.974089</v>
+        <v>0.76251</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core 128</t>
+          <t>Model_LightSpeed VCT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2883</v>
+        <v>-1.0968</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.3339</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1242</v>
+        <v>0.0274</v>
       </c>
       <c r="E21" t="n">
-        <v>4.522</v>
+        <v>4.0721</v>
       </c>
       <c r="F21" t="n">
-        <v>0.917</v>
+        <v>1.276</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3144</v>
+        <v>-0.8596</v>
       </c>
       <c r="H21" t="n">
-        <v>0.753206</v>
+        <v>0.390034</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Model_LightSpeed VCT</t>
+          <t>Model_LightSpeed16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.1135</v>
+        <v>-9.3827</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3284</v>
+        <v>0.0001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0272</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>3.9711</v>
+        <v>4.02698873775208e+51</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2717</v>
+        <v>65.4132</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8756</v>
+        <v>-0.1434</v>
       </c>
       <c r="H22" t="n">
-        <v>0.381265</v>
+        <v>0.885945</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Model_LightSpeed16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-9.320499999999999</v>
+        <v>15.2945</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001</v>
+        <v>4388451.0421</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
-        <v>9.083631727057405e+51</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>65.79649999999999</v>
+        <v>1797.9039</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1417</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.887352</v>
+        <v>0.993213</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.0399</v>
+        <v>-0.3791</v>
       </c>
       <c r="C24" t="n">
-        <v>3402110.5545</v>
+        <v>0.6845</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.1117</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.1927</v>
       </c>
       <c r="F24" t="n">
-        <v>1620.4455</v>
+        <v>0.9248</v>
       </c>
       <c r="G24" t="n">
-        <v>0.009299999999999999</v>
+        <v>-0.41</v>
       </c>
       <c r="H24" t="n">
-        <v>0.992595</v>
+        <v>0.68182</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3897</v>
+        <v>11.6472</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6773</v>
+        <v>114367.4289</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1117</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4.1082</v>
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>0.9197</v>
+        <v>482.4509</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4237</v>
+        <v>0.0241</v>
       </c>
       <c r="H25" t="n">
-        <v>0.671805</v>
+        <v>0.9807399999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11.6828</v>
+        <v>1.9232</v>
       </c>
       <c r="C26" t="n">
-        <v>118513.828</v>
+        <v>6.8428</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.217</v>
+      </c>
+      <c r="E26" t="n">
+        <v>215.8074</v>
       </c>
       <c r="F26" t="n">
-        <v>484.9425</v>
+        <v>1.7608</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0241</v>
+        <v>1.0922</v>
       </c>
       <c r="H26" t="n">
-        <v>0.98078</v>
+        <v>0.274742</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9836</v>
+        <v>-16.9386</v>
       </c>
       <c r="C27" t="n">
-        <v>7.2688</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="E27" t="n">
-        <v>242.3395</v>
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>1.7892</v>
+        <v>1587.7706</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1087</v>
+        <v>-0.0107</v>
       </c>
       <c r="H27" t="n">
-        <v>0.267581</v>
+        <v>0.991488</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-16.2072</v>
+        <v>0.0541</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.0556</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.174</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6.4055</v>
       </c>
       <c r="F28" t="n">
-        <v>1187.4477</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0136</v>
+        <v>0.0588</v>
       </c>
       <c r="H28" t="n">
-        <v>0.98911</v>
+        <v>0.953084</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0532</v>
+        <v>0.2107</v>
       </c>
       <c r="C29" t="n">
-        <v>1.0546</v>
+        <v>1.2346</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1756</v>
+        <v>0.0872</v>
       </c>
       <c r="E29" t="n">
-        <v>6.3318</v>
+        <v>17.4888</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9145</v>
+        <v>1.3525</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0581</v>
+        <v>0.1558</v>
       </c>
       <c r="H29" t="n">
-        <v>0.953655</v>
+        <v>0.876181</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3105</v>
+        <v>-0.8439</v>
       </c>
       <c r="C30" t="n">
-        <v>1.3641</v>
+        <v>0.43</v>
       </c>
       <c r="D30" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0462</v>
       </c>
       <c r="E30" t="n">
-        <v>19.2611</v>
+        <v>4.006</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3509</v>
+        <v>1.1386</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2298</v>
+        <v>-0.7411</v>
       </c>
       <c r="H30" t="n">
-        <v>0.818225</v>
+        <v>0.45861</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8307</v>
+        <v>-0.3831</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4357</v>
+        <v>0.6817</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0471</v>
+        <v>0.0333</v>
       </c>
       <c r="E31" t="n">
-        <v>4.028</v>
+        <v>13.9595</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1347</v>
+        <v>1.5405</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.7321</v>
+        <v>-0.2487</v>
       </c>
       <c r="H31" t="n">
-        <v>0.464106</v>
+        <v>0.803597</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3334</v>
+        <v>-8.7904</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7165</v>
+        <v>0.0002</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0353</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>14.532</v>
+        <v>1.195989126779547e+44</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5356</v>
+        <v>56.2679</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2171</v>
+        <v>-0.1562</v>
       </c>
       <c r="H32" t="n">
-        <v>0.828138</v>
+        <v>0.875856</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-8.835900000000001</v>
+        <v>-8.525600000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>8.090972069683324e+45</v>
+        <v>3.999401854126652e+38</v>
       </c>
       <c r="F33" t="n">
-        <v>58.4414</v>
+        <v>49.6999</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1512</v>
+        <v>-0.1715</v>
       </c>
       <c r="H33" t="n">
-        <v>0.879823</v>
+        <v>0.863797</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-8.588200000000001</v>
+        <v>-6.3876</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0002</v>
+        <v>0.0017</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>4.168248213930226e+40</v>
+        <v>2.907855940559166e+18</v>
       </c>
       <c r="F34" t="n">
-        <v>52.1026</v>
+        <v>24.9502</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1648</v>
+        <v>-0.256</v>
       </c>
       <c r="H34" t="n">
-        <v>0.869075</v>
+        <v>0.797939</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-6.4234</v>
+        <v>-9.053000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0016</v>
+        <v>0.0001</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.968356210021403e+19</v>
+        <v>3.424597051506435e+48</v>
       </c>
       <c r="F35" t="n">
-        <v>25.9442</v>
+        <v>61.6379</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2476</v>
+        <v>-0.1469</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8044559999999999</v>
+        <v>0.883231</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-9.109500000000001</v>
+        <v>0.3628</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0001</v>
+        <v>1.4374</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.2357</v>
       </c>
       <c r="E36" t="n">
-        <v>9.852499195344899e+50</v>
+        <v>8.764200000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>64.55549999999999</v>
+        <v>0.9224</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1411</v>
+        <v>0.3934</v>
       </c>
       <c r="H36" t="n">
-        <v>0.887782</v>
+        <v>0.694041</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_iCT 128</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3797</v>
+        <v>24.1618</v>
       </c>
       <c r="C37" t="n">
-        <v>1.4618</v>
+        <v>31142442391.664</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2423</v>
-      </c>
-      <c r="E37" t="n">
-        <v>8.818899999999999</v>
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0.917</v>
+        <v>37526.8183</v>
       </c>
       <c r="G37" t="n">
-        <v>0.414</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>0.678849</v>
+        <v>0.999486</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_iCT 128</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>23.8806</v>
+        <v>-13.3936</v>
       </c>
       <c r="C38" t="n">
-        <v>23506857810.2528</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1737,43 +1717,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>33203.1864</v>
+        <v>384.3958</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0007</v>
+        <v>-0.0348</v>
       </c>
       <c r="H38" t="n">
-        <v>0.999426</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Model_iCT 256</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>-13.572</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>418.6559</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-0.0324</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.974139</v>
+        <v>0.972205</v>
       </c>
     </row>
   </sheetData>
@@ -1859,7 +1809,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7518</v>
+        <v>0.7514</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1874,7 +1824,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7268</v>
+        <v>0.7258</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1889,7 +1839,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7778</v>
+        <v>0.7775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1915,7 +1865,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2455</v>
+        <v>0.236</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
@@ -1926,7 +1876,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7075</v>
+        <v>0.735</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1941,7 +1891,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6803</v>
+        <v>0.652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1956,7 +1906,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4101</v>
+        <v>0.3989</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,7 +1921,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.881</v>
+        <v>0.8868</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,7 +1936,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C14" t="inlineStr"/>
     </row>
@@ -1997,7 +1947,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>866</v>
+        <v>830</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -2008,7 +1958,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -2019,7 +1969,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -2030,7 +1980,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.346</v>
+        <v>6.4095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2045,7 +1995,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.824635</v>
+        <v>0.601464</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2073,7 +2023,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2145</v>
+        <v>0.2135</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2088,7 +2038,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1556</v>
+        <v>0.1557</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2103,7 +2053,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1658.03</v>
+        <v>1657.3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2118,7 +2068,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1864.08</v>
+        <v>1857.93</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2133,7 +2083,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" t="inlineStr"/>
     </row>
